--- a/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>BCSF</t>
   </si>
@@ -656,305 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E8" s="3">
         <v>72400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>74700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>58400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>52400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>46500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>48300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>47900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>51500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>54800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>52700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>50600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>39900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>21400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E9" s="3">
         <v>33700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>34000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>23200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>32200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,85 +971,88 @@
         <v>38700</v>
       </c>
       <c r="E10" s="3">
+        <v>38700</v>
+      </c>
+      <c r="F10" s="3">
         <v>41700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>34500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>23300</v>
       </c>
       <c r="M10" s="3">
         <v>23300</v>
       </c>
       <c r="N10" s="3">
+        <v>23300</v>
+      </c>
+      <c r="O10" s="3">
         <v>23700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23900</v>
-      </c>
-      <c r="S10" s="3">
-        <v>22600</v>
       </c>
       <c r="T10" s="3">
         <v>22600</v>
       </c>
       <c r="U10" s="3">
+        <v>22600</v>
+      </c>
+      <c r="V10" s="3">
         <v>22900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1157,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1329,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E17" s="3">
         <v>36100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>37300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E18" s="3">
         <v>36300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>30100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>21700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>22100</v>
       </c>
       <c r="O18" s="3">
         <v>22100</v>
       </c>
       <c r="P18" s="3">
+        <v>22100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>21400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21300</v>
-      </c>
-      <c r="T18" s="3">
-        <v>21200</v>
       </c>
       <c r="U18" s="3">
         <v>21200</v>
       </c>
       <c r="V18" s="3">
+        <v>21200</v>
+      </c>
+      <c r="W18" s="3">
         <v>21300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>19700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,94 +1680,98 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>23300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>20500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>17600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>30000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-127000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>18100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-29600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1820,8 +1856,11 @@
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1906,111 +1945,117 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E23" s="3">
         <v>34500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>33700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>42400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>39700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>51500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-104400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>39300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>19000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>8</v>
@@ -2018,11 +2063,11 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>8</v>
@@ -2030,11 +2075,11 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>8</v>
@@ -2042,17 +2087,17 @@
       <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="S24" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2069,8 +2114,8 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>8</v>
+      <c r="AB24" s="3">
+        <v>0</v>
       </c>
       <c r="AC24" s="3" t="s">
         <v>8</v>
@@ -2078,8 +2123,11 @@
       <c r="AD24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E26" s="3">
         <v>33900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>43500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>33700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>22300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>51500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-104400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>39300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E27" s="3">
         <v>33900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>43500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>33700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>22300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>39500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>51500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-104400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>18200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>39300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-23300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-20500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-17600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>127000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-18100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>29600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E33" s="3">
         <v>33900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>43500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>33700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>22300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>39500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>51500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-104400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>18200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E35" s="3">
         <v>33900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>43500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>33700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>22300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>39500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>51500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-104400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>18200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E41" s="3">
         <v>79500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>92300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>117400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>37700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>55800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>71600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>101000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>80600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>152700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>141000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>122700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>140900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>20400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>168200</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,94 +3440,100 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E43" s="3">
         <v>16100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>109700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>119600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2500</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
-      </c>
       <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
         <v>170500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3523,43 +3618,46 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
@@ -3573,8 +3671,8 @@
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="S45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3595,22 +3693,25 @@
         <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
         <v>100</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
       <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3695,94 +3796,100 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2335500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2429500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2425700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2448500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2421300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2334300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2329900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2182400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2313700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2381700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2339700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2351800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2500200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2479900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2495300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2512600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2550600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2534600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2441300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1844000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1743400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1361500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1077200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>918400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>834500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>485200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>419400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>195200</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3867,8 +3974,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3953,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E52" s="3">
         <v>28900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>69700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>36100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>88300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>58700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>77700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>82400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>34700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>89900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2472300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2566500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2675400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2606400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2592400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2521400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2426000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2310600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2571200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2498700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2449300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2491300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2603500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2621100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2610000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2604300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2645600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2727500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2589800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1995900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1791000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1564800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1233200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1061100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>988300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>528800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>613400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>367700</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,94 +4576,98 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>1100</v>
       </c>
       <c r="AA57" s="3">
         <v>1100</v>
       </c>
       <c r="AB57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC57" s="3">
         <v>1400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4619,94 +4752,100 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E59" s="3">
         <v>57500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>53800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>87800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>61300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>71400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>105900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>50100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>53900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>49100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>59900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>153200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>80100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>25600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>30400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4791,94 +4930,100 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1255900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1370300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1489600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1408000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1385300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1359600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1244300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1090700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1415000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1346200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1306000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1341900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1458400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1513900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1542300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1654900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1574600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1657600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1505100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>914900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>634900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>597300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>446500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>389400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>451000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>76300</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4963,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1335900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1434000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1549600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1485200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1476000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1425300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1319000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1198900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1471200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1399000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1351000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1413500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1535500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1570700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1589100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1711600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1627200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1709200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1568600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>976100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>789400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>680900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>478600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>426700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>481300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>109000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-35900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-47300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-52100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-72300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-61400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-56700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-68400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-66800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-68200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-88700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-98500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-116300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-145800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-145600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-20000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-19400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-16400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-32700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>-600</v>
       </c>
       <c r="AC72" s="3">
         <v>-600</v>
       </c>
       <c r="AD72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1136500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1132500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1125800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1121100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1116400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1096100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1107000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1111700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1100000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1099700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1098300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1077800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1068000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1050500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1021000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>892800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1018400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1018200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1021200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1019800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1001600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>884000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>754600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>634500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>507000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>506900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>504500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>339500</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E81" s="3">
         <v>33900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>43500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>33700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>22300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>39500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>51500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-104400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>18200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6494,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E89" s="3">
         <v>122300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-43000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>63100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-99700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-178400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-101800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>174800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>72800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-51400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-102100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>39800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-197100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-326800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-216400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-155100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-75900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-339000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-69000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-222300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7261,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7128,8 +7348,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7526,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7386,8 +7615,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,22 +7650,23 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-24500</v>
+        <v>-27100</v>
       </c>
       <c r="E96" s="3">
         <v>-24500</v>
       </c>
       <c r="F96" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="G96" s="3">
         <v>-23200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-22000</v>
       </c>
       <c r="H96" s="3">
         <v>-22000</v>
@@ -7463,7 +7696,7 @@
         <v>-22000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-21200</v>
+        <v>-22000</v>
       </c>
       <c r="R96" s="3">
         <v>-21200</v>
@@ -7475,14 +7708,14 @@
         <v>-21200</v>
       </c>
       <c r="U96" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-17800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-21100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7504,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-142100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-144500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>131800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>43700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-58500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-138900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-78500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>57900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-106700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>131600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>258600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>169700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>266000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>173900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>57400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>441200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>86600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>74800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>168300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>700</v>
       </c>
       <c r="I101" s="3">
         <v>700</v>
       </c>
       <c r="J101" s="3">
+        <v>700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
-      </c>
-      <c r="P101" s="3">
-        <v>200</v>
       </c>
       <c r="Q101" s="3">
         <v>200</v>
       </c>
       <c r="R101" s="3">
+        <v>200</v>
+      </c>
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-100</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
       </c>
       <c r="Y101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-44600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>110700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-42200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-89200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>29100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>34300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>61400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-157200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>49500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>102400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-147800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>101400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>BCSF</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E8" s="3">
         <v>74900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>72400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>74700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>52400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>48300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>47900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>51500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>54800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>52700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>50600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>39900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>33700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E9" s="3">
         <v>36200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>23600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>32200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>38700</v>
+        <v>37600</v>
       </c>
       <c r="E10" s="3">
         <v>38700</v>
       </c>
       <c r="F10" s="3">
+        <v>38700</v>
+      </c>
+      <c r="G10" s="3">
         <v>41700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>34500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>23300</v>
       </c>
       <c r="N10" s="3">
         <v>23300</v>
       </c>
       <c r="O10" s="3">
+        <v>23300</v>
+      </c>
+      <c r="P10" s="3">
         <v>23700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23900</v>
-      </c>
-      <c r="T10" s="3">
-        <v>22600</v>
       </c>
       <c r="U10" s="3">
         <v>22600</v>
       </c>
       <c r="V10" s="3">
+        <v>22600</v>
+      </c>
+      <c r="W10" s="3">
         <v>22900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>5100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E17" s="3">
         <v>39000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>29500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>31500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E18" s="3">
         <v>35900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>36300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>21700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>22100</v>
       </c>
       <c r="P18" s="3">
         <v>22100</v>
       </c>
       <c r="Q18" s="3">
+        <v>22100</v>
+      </c>
+      <c r="R18" s="3">
         <v>21400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21300</v>
-      </c>
-      <c r="U18" s="3">
-        <v>21200</v>
       </c>
       <c r="V18" s="3">
         <v>21200</v>
       </c>
       <c r="W18" s="3">
+        <v>21200</v>
+      </c>
+      <c r="X18" s="3">
         <v>21300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,97 +1714,101 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>23300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-19000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-127000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>18100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-29600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1859,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E23" s="3">
         <v>32100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>42400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>31800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>39700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>51500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-104400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>39300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>11400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2046,19 +2092,19 @@
         <v>1000</v>
       </c>
       <c r="E24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>8</v>
@@ -2066,11 +2112,11 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>8</v>
@@ -2078,11 +2124,11 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>8</v>
@@ -2090,17 +2136,17 @@
       <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2117,8 +2163,8 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>8</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>8</v>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E26" s="3">
         <v>31100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>43500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>33700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>22300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>39500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>51500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-104400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>39300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E27" s="3">
         <v>31100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>33900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>43500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>39500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>51500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-104400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>39300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>6900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-23300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>19000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-30000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>127000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-18100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>29600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E33" s="3">
         <v>31100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>33900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>39500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>51500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-104400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>39300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E35" s="3">
         <v>31100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>33900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>39500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>51500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-104400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>39300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E41" s="3">
         <v>49400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>79500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>92300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>44200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>117400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>55800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>71600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>101000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>80600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>152700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>141000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>122700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>140900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>168200</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,97 +3533,103 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E43" s="3">
         <v>13700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>68400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>119600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>29100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2500</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
-      </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
         <v>170500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,46 +3717,49 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
       <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
@@ -3674,8 +3773,8 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3696,22 +3795,25 @@
         <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
       </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
       </c>
       <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,97 +3901,103 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2437000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2335500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2429500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2425700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2448500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2421300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2334300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2329900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2182400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2313700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2381700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2339700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2351800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2500200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2479900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2495300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2512600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2550600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2534600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2441300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1844000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1743400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1361500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1077200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>918400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>834500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>485200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>419400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>195200</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E52" s="3">
         <v>65900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>69700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>36100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>88300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>82400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>34700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>89900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2580100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2472300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2566500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2675400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2606400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2592400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2521400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2426000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2310600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2571200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2498700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2449300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2491300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2603500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2621100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2610000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2604300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2645600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2727500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2589800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1995900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1791000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1564800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1233200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1061100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>988300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>528800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>613400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>367700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4707,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E57" s="3">
         <v>9600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>1100</v>
       </c>
       <c r="AB57" s="3">
         <v>1100</v>
       </c>
       <c r="AC57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD57" s="3">
         <v>1400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,97 +4889,103 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E59" s="3">
         <v>68100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>87800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>71400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>105900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>53900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>59900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>58900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>153200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>80100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>30900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>33600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>25600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>30400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,97 +5073,103 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1357600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1255900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1370300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1489600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1408000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1385300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1359600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1244300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1090700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1415000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1346200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1306000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1341900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1458400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1513900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1542300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1654900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1574600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1657600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1505100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>914900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>634900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>597300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>446500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>389400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>451000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>76300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1437600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1335900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1434000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1549600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1485200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1476000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1425300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1319000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1198900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1471200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1399000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1351000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1413500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1535500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1570700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1589100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1711600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1627200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1709200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1568600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>976100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>789400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>680900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>478600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>426700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>481300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>109000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-35900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-72300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-61400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-56700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-68400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-66800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-68200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-88700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-98500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-116300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-145800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-145600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-20000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-19400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-16400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-32700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AC72" s="3">
-        <v>-600</v>
       </c>
       <c r="AD72" s="3">
         <v>-600</v>
       </c>
       <c r="AE72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1142500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1136500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1132500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1125800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1121100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1116400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1096100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1107000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1111700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1100000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1099700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1098300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1077800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1068000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1050500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1021000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>892800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1018400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1018200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1021200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1019800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1001600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>884000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>754600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>634500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>507000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>506900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>504500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>339500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E81" s="3">
         <v>31100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>33900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>39500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>51500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-104400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>39300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-63700</v>
+      </c>
+      <c r="E89" s="3">
         <v>148700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>122300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-43000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>63100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-99700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-178400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-101800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>69100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>174800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-51400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-102100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>39800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-197100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-326800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-216400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-155100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-75900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-339000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-69000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-222300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7660,16 +7894,16 @@
         <v>-27100</v>
       </c>
       <c r="E96" s="3">
-        <v>-24500</v>
+        <v>-27100</v>
       </c>
       <c r="F96" s="3">
         <v>-24500</v>
       </c>
       <c r="G96" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="H96" s="3">
         <v>-23200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-22000</v>
       </c>
       <c r="I96" s="3">
         <v>-22000</v>
@@ -7699,7 +7933,7 @@
         <v>-22000</v>
       </c>
       <c r="R96" s="3">
-        <v>-21200</v>
+        <v>-22000</v>
       </c>
       <c r="S96" s="3">
         <v>-21200</v>
@@ -7711,14 +7945,14 @@
         <v>-21200</v>
       </c>
       <c r="V96" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="W96" s="3">
         <v>-17800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-21100</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8250,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-142100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-144500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>88900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>131800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>43700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-58500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-138900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-78500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-52000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>57900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-106700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>131600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>258600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>169700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>266000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>173900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>57400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>441200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>86600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>74800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>168300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>700</v>
       </c>
       <c r="J101" s="3">
         <v>700</v>
       </c>
       <c r="K101" s="3">
+        <v>700</v>
+      </c>
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>200</v>
       </c>
       <c r="R101" s="3">
         <v>200</v>
       </c>
       <c r="S101" s="3">
+        <v>200</v>
+      </c>
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-100</v>
       </c>
       <c r="Y101" s="3">
         <v>-100</v>
       </c>
       <c r="Z101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E102" s="3">
         <v>7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>47500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-44600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-88700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>110700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-25700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>28400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-89200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>29100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>34300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-157200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>49500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>102400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-147800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>101400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCSF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>BCSF</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E8" s="3">
         <v>74500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>74900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>72400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>74700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>58800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>52400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>48300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>47900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>51500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>54800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>52700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>50600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>21400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E9" s="3">
         <v>36900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>36200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>32200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>30100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E10" s="3">
         <v>37600</v>
-      </c>
-      <c r="E10" s="3">
-        <v>38700</v>
       </c>
       <c r="F10" s="3">
         <v>38700</v>
       </c>
       <c r="G10" s="3">
+        <v>38700</v>
+      </c>
+      <c r="H10" s="3">
         <v>41700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23200</v>
-      </c>
-      <c r="N10" s="3">
-        <v>23300</v>
       </c>
       <c r="O10" s="3">
         <v>23300</v>
       </c>
       <c r="P10" s="3">
+        <v>23300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>23700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23900</v>
-      </c>
-      <c r="U10" s="3">
-        <v>22600</v>
       </c>
       <c r="V10" s="3">
         <v>22600</v>
       </c>
       <c r="W10" s="3">
+        <v>22600</v>
+      </c>
+      <c r="X10" s="3">
         <v>22900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>14000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E17" s="3">
         <v>39500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E18" s="3">
         <v>35000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>40000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>21100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21900</v>
-      </c>
-      <c r="P18" s="3">
-        <v>22100</v>
       </c>
       <c r="Q18" s="3">
         <v>22100</v>
       </c>
       <c r="R18" s="3">
+        <v>22100</v>
+      </c>
+      <c r="S18" s="3">
         <v>21400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>21200</v>
       </c>
       <c r="W18" s="3">
         <v>21200</v>
       </c>
       <c r="X18" s="3">
+        <v>21200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>21300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,100 +1748,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>23300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>17600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>30000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-127000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-29600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,123 +2031,129 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E23" s="3">
         <v>36100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>30300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>39700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>51500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-104400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>19200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>11400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>7200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E24" s="3">
         <v>1000</v>
       </c>
       <c r="F24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>8</v>
@@ -2115,11 +2161,11 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>8</v>
@@ -2127,11 +2173,11 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>8</v>
@@ -2139,17 +2185,17 @@
       <c r="T24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="s">
+      <c r="U24" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2166,8 +2212,8 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>8</v>
+      <c r="AD24" s="3">
+        <v>0</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>8</v>
@@ -2175,8 +2221,11 @@
       <c r="AF24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E26" s="3">
         <v>35100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>33900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>33700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>22300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>42400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>39500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>51500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-104400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>39300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>6900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E27" s="3">
         <v>35100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>33900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>43500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>33700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>39500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>51500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>21800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-104400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>21400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>6900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-23300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-17600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-30000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>127000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>29600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E33" s="3">
         <v>35100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>33900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>43500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>33700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>39500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>51500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>21800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-104400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E35" s="3">
         <v>35100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>33900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>43500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>33700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>39500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>51500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>21800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-104400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E41" s="3">
         <v>48900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>79500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>92300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>59800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>80800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>117400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>35100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>55800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>71600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>101000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>80600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>15300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>152700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>141000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>122700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>140900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>20400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>168200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3626,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E43" s="3">
         <v>9300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>16100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>109700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>68400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>119600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>48700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>29100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>10300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2500</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
       <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
         <v>170500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,49 +3816,52 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
@@ -3776,8 +3875,8 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3798,22 +3897,25 @@
         <v>0</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
       </c>
       <c r="AD45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
       </c>
       <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,100 +4006,106 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2272500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2437000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2335500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2429500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2425700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2448500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2421300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2334300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2329900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2182400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2313700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2381700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2339700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2351800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2500200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2479900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2495300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2512600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2550600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2534600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2441300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1844000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1743400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1361500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1077200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>918400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>834500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>485200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>419400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>195200</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4088,8 +4196,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E52" s="3">
         <v>76100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>65900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>36100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>88300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>77700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>82400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>22600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>34700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>89900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>31800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>43600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2414800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2580100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2472300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2566500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2675400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2606400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2592400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2521400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2426000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2310600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2571200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2498700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2449300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2491300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2603500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2621100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2610000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2604300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2645600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2727500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2589800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1995900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1791000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1564800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1233200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1061100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>988300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>528800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>613400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>367700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E57" s="3">
         <v>9300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>1100</v>
       </c>
       <c r="AC57" s="3">
         <v>1100</v>
       </c>
       <c r="AD57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE57" s="3">
         <v>1400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,100 +5026,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E59" s="3">
         <v>68800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>53800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>73500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>87800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>105900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>49100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>51300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>46100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>53900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>59900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>58900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>153200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>80100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>30900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>25600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>30400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,100 +5216,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1173900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1357600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1255900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1370300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1489600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1408000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1385300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1359600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1244300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1090700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1415000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1346200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1306000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1341900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1458400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1513900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1542300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1654900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1574600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1657600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1505100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>914900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>634900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>597300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>446500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>389400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>451000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>76300</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1272300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1437600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1335900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1434000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1549600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1485200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1476000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1425300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1319000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1198900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1471200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1399000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1351000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1413500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1535500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1570700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1589100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1711600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1627200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1709200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1568600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>976100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>789400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>680900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>478600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>426700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>481300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>21900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>109000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6201,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6039,91 +6213,94 @@
         <v>-22700</v>
       </c>
       <c r="E72" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-32000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-35900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-52100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-72300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-61400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-56700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-68400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-66800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-68200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-88700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-98500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-116300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-145800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-145600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-20000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-19400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-16400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-32700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-17400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3400</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>-600</v>
       </c>
       <c r="AE72" s="3">
         <v>-600</v>
       </c>
       <c r="AF72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AG72" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,8 +6581,11 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6407,91 +6593,94 @@
         <v>1142500</v>
       </c>
       <c r="E76" s="3">
+        <v>1142500</v>
+      </c>
+      <c r="F76" s="3">
         <v>1136500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1132500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1125800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1121100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1116400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1096100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1107000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1111700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1100000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1099700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1098300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1077800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1068000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1050500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1021000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>892800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1018400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1018200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1021200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1019800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1001600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>884000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>754600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>634500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>507000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>506900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>504500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>339500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E81" s="3">
         <v>35100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>33900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>43500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>33700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>39500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>51500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>21800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-104400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>192400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-63700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>148700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>122300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-43000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>63100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-99700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-178400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-101800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>69100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>174800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>35800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>72800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-51400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-102100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>39800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-197100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-326800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-216400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-155100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-75900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-339000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-69000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-222300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7986,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,28 +8118,29 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-27100</v>
+        <v>-29100</v>
       </c>
       <c r="E96" s="3">
         <v>-27100</v>
       </c>
       <c r="F96" s="3">
-        <v>-24500</v>
+        <v>-27100</v>
       </c>
       <c r="G96" s="3">
         <v>-24500</v>
       </c>
       <c r="H96" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="I96" s="3">
         <v>-23200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-22000</v>
       </c>
       <c r="J96" s="3">
         <v>-22000</v>
@@ -7936,7 +8170,7 @@
         <v>-22000</v>
       </c>
       <c r="S96" s="3">
-        <v>-21200</v>
+        <v>-22000</v>
       </c>
       <c r="T96" s="3">
         <v>-21200</v>
@@ -7948,14 +8182,14 @@
         <v>-21200</v>
       </c>
       <c r="W96" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="X96" s="3">
         <v>-17800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-216500</v>
+      </c>
+      <c r="E100" s="3">
         <v>73900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-142100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-144500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>88900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>131800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>43700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-58500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-138900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-78500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-52000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>57900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-106700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>131600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>258600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>169700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>266000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>173900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>57400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>441200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>86600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>74800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>168300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>700</v>
       </c>
       <c r="K101" s="3">
         <v>700</v>
       </c>
       <c r="L101" s="3">
+        <v>700</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
-      </c>
-      <c r="R101" s="3">
-        <v>200</v>
       </c>
       <c r="S101" s="3">
         <v>200</v>
       </c>
       <c r="T101" s="3">
+        <v>200</v>
+      </c>
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-100</v>
       </c>
       <c r="Z101" s="3">
         <v>-100</v>
       </c>
       <c r="AA101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E102" s="3">
         <v>10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-44600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>66900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-88700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>110700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-25700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-42200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>21000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>28400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-89200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>29100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>34300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>61400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-157200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>49500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>102400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-147800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>101400</v>
       </c>
     </row>
